--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.94620913929047</v>
+        <v>10.0662589851347</v>
       </c>
       <c r="D2" t="n">
-        <v>61.22305949837166</v>
+        <v>9.948747168485395</v>
       </c>
       <c r="E2" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F2" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.14007512071589</v>
+        <v>10.42276220711633</v>
       </c>
       <c r="D3" t="n">
-        <v>63.03456319875784</v>
+        <v>10.24311651979815</v>
       </c>
       <c r="E3" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F3" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>69.79941668339868</v>
+        <v>11.34240521105228</v>
       </c>
       <c r="D4" t="n">
-        <v>69.51333023737116</v>
+        <v>11.29591616357281</v>
       </c>
       <c r="E4" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F4" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.70764830560246</v>
+        <v>9.0524928496604</v>
       </c>
       <c r="D5" t="n">
-        <v>54.9319742714397</v>
+        <v>8.926445819108951</v>
       </c>
       <c r="E5" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F5" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>49.30874563007237</v>
+        <v>8.012671164886759</v>
       </c>
       <c r="D6" t="n">
-        <v>48.34138789355645</v>
+        <v>7.855475532702924</v>
       </c>
       <c r="E6" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F6" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.75172394286398</v>
+        <v>9.059655140715398</v>
       </c>
       <c r="D7" t="n">
-        <v>55.28117983299606</v>
+        <v>8.983191722861861</v>
       </c>
       <c r="E7" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F7" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.89269372004128</v>
+        <v>9.082562729506709</v>
       </c>
       <c r="D8" t="n">
-        <v>55.70072107610496</v>
+        <v>9.051367174867057</v>
       </c>
       <c r="E8" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F8" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.94910976531067</v>
+        <v>9.254230336862985</v>
       </c>
       <c r="D9" t="n">
-        <v>57.07861717107289</v>
+        <v>9.275275290299346</v>
       </c>
       <c r="E9" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F9" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.74198099091394</v>
+        <v>4.670571911023516</v>
       </c>
       <c r="D10" t="n">
-        <v>28.43003903253618</v>
+        <v>4.61988134278713</v>
       </c>
       <c r="E10" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F10" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>29.54578431933576</v>
+        <v>4.801189951892061</v>
       </c>
       <c r="D11" t="n">
-        <v>28.67037907648462</v>
+        <v>4.658936599928751</v>
       </c>
       <c r="E11" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F11" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.70672172962287</v>
+        <v>2.064842281063716</v>
       </c>
       <c r="D12" t="n">
-        <v>13.63968372282161</v>
+        <v>2.216448604958511</v>
       </c>
       <c r="E12" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F12" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.88009859652465</v>
+        <v>6.318016021935256</v>
       </c>
       <c r="D13" t="n">
-        <v>39.60691043643184</v>
+        <v>6.436122945920174</v>
       </c>
       <c r="E13" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F13" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.87351191519573</v>
+        <v>6.479445686219307</v>
       </c>
       <c r="D14" t="n">
-        <v>40.86321491017458</v>
+        <v>6.64027242290337</v>
       </c>
       <c r="E14" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F14" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.47393520624347</v>
+        <v>5.439514471014563</v>
       </c>
       <c r="D15" t="n">
-        <v>34.53658253480953</v>
+        <v>5.61219466190655</v>
       </c>
       <c r="E15" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F15" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>43.14354594767397</v>
+        <v>7.01082621649702</v>
       </c>
       <c r="D16" t="n">
-        <v>43.63165409887608</v>
+        <v>7.090143791067364</v>
       </c>
       <c r="E16" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F16" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>41.71699052813111</v>
+        <v>6.779010960821306</v>
       </c>
       <c r="D17" t="n">
-        <v>42.53079716616337</v>
+        <v>6.911254539501547</v>
       </c>
       <c r="E17" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F17" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>69.25049715582132</v>
+        <v>11.25320578782097</v>
       </c>
       <c r="D18" t="n">
-        <v>69.46276898036346</v>
+        <v>11.28769995930906</v>
       </c>
       <c r="E18" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F18" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>65.28328896917031</v>
+        <v>10.60853445749018</v>
       </c>
       <c r="D19" t="n">
-        <v>66.39541914776578</v>
+        <v>10.78925561151194</v>
       </c>
       <c r="E19" t="n">
-        <v>15.49331308920772</v>
+        <v>2.517663376996255</v>
       </c>
       <c r="F19" t="n">
-        <v>15.25736818211875</v>
+        <v>2.479322329594297</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
